--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487647_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487647_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8106</v>
+        <v>4.5192</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6216</v>
+        <v>5.2212</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.702</v>
       </c>
       <c r="G2" t="n">
         <v>3.9296</v>
@@ -610,13 +610,13 @@
         <v>0.9702</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9094</v>
+        <v>0.618</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5473</v>
+        <v>0.1469</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3621</v>
+        <v>0.4711</v>
       </c>
       <c r="V2" t="n">
         <v>0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.9365</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2597</v>
+        <v>1.4599</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3403</v>
+        <v>1.4765</v>
       </c>
       <c r="G3" t="n">
         <v>2.1211</v>
@@ -688,13 +688,13 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.4273</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0606</v>
+        <v>0.1396</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1514</v>
+        <v>0.2877</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.019</v>
+        <v>2.034</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7796</v>
+        <v>0.7401</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2394</v>
+        <v>1.2939</v>
       </c>
       <c r="G4" t="n">
         <v>2.1285</v>
@@ -766,13 +766,13 @@
         <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6667</v>
+        <v>0.6816</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.12</v>
+        <v>-0.1596</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7867</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4454</v>
+        <v>2.0253</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3183</v>
+        <v>2.0397</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7637</v>
+        <v>-0.0144</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4086</v>
+        <v>2.9996</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1351</v>
+        <v>0.2752</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5437</v>
+        <v>2.7245</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2707</v>
+        <v>3.515</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1895</v>
+        <v>2.381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.134</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1379</v>
+        <v>-0.5154</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3246</v>
+        <v>-2.1058</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4626</v>
+        <v>1.5904</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.3421</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2412</v>
+        <v>-0.429</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7436</v>
+        <v>0.7711</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6597</v>
+        <v>-0.7343</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3776</v>
+        <v>0.894</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4132</v>
+        <v>1.6767</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8427</v>
+        <v>1.1613</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2559</v>
+        <v>0.5154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9846</v>
+        <v>1.7959</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.379</v>
+        <v>-2.0152</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3636</v>
+        <v>3.8111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0965</v>
+        <v>2.2997</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0659</v>
+        <v>-0.3213</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1624</v>
+        <v>2.621</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8881</v>
+        <v>-0.5038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3131</v>
+        <v>-1.6939</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2012</v>
+        <v>1.1901</v>
       </c>
       <c r="P6" t="n">
         <v>0.194</v>
@@ -922,28 +922,28 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3569</v>
+        <v>0.4212</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9691</v>
+        <v>-0.1683</v>
       </c>
       <c r="U6" t="n">
-        <v>1.326</v>
+        <v>0.5894</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1224</v>
+        <v>-0.7343</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1224</v>
+        <v>-0.7343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0704</v>
+        <v>1.3697</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4391</v>
+        <v>-1.2577</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3687</v>
+        <v>2.6274</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9996</v>
+        <v>1.4086</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2752</v>
+        <v>-0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7245</v>
+        <v>1.5437</v>
       </c>
       <c r="J7" t="n">
-        <v>3.515</v>
+        <v>0.2707</v>
       </c>
       <c r="K7" t="n">
-        <v>2.381</v>
+        <v>0.1895</v>
       </c>
       <c r="L7" t="n">
-        <v>1.134</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5154</v>
+        <v>1.1379</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1058</v>
+        <v>-0.3246</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5904</v>
+        <v>1.4626</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6128</v>
+        <v>0.4268</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0296</v>
+        <v>-0.1806</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4168</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7343</v>
+        <v>-0.6597</v>
       </c>
       <c r="W7" t="n">
-        <v>0.894</v>
+        <v>-0.3776</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6283</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0319</v>
+        <v>1.3285</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2608</v>
+        <v>-1.6821</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2927</v>
+        <v>3.0106</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9579</v>
+        <v>0.9846</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0488</v>
+        <v>-0.379</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9091</v>
+        <v>1.3636</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3598</v>
+        <v>0.0965</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3192</v>
+        <v>-0.0659</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>0.1624</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5981</v>
+        <v>0.8881</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2704</v>
+        <v>-0.3131</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8685</v>
+        <v>1.2012</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7164</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2905</v>
+        <v>0.2723</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3623</v>
+        <v>-0.8084</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6528</v>
+        <v>1.0807</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5</v>
+        <v>-0.1224</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-0.1224</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6307</v>
+        <v>0.429</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3605</v>
+        <v>-2.4004</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2701</v>
+        <v>2.8294</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7959</v>
+        <v>2.9579</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0152</v>
+        <v>1.0488</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8111</v>
+        <v>1.9091</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2997</v>
+        <v>2.3598</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3213</v>
+        <v>2.3192</v>
       </c>
       <c r="L9" t="n">
-        <v>2.621</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5038</v>
+        <v>0.5981</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6939</v>
+        <v>-1.2704</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1901</v>
+        <v>1.8685</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R9" t="n">
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6249</v>
+        <v>0.6875</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9691</v>
+        <v>-0.5019</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3441</v>
+        <v>1.1895</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7343</v>
+        <v>-0.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7343</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3954</v>
+        <v>-0.2803</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7473</v>
+        <v>-0.6867</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3519</v>
+        <v>0.4064</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4317</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1577</v>
+        <v>-0.0426</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1211</v>
+        <v>-0.0606</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0366</v>
+        <v>0.0179</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6312</v>
+        <v>-0.6857</v>
       </c>
       <c r="E11" t="n">
         <v>-1.1519</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5206</v>
+        <v>0.4661</v>
       </c>
       <c r="G11" t="n">
         <v>0.1219</v>
@@ -1312,13 +1312,13 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1454</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3271</v>
+        <v>0.2725</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1224</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8649</v>
+        <v>-2.9204</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8372</v>
+        <v>-3.8382</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6157</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0374</v>
+        <v>0.9819</v>
       </c>
       <c r="T12" t="n">
-        <v>1.578</v>
+        <v>0.577</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4594</v>
+        <v>0.4049</v>
       </c>
       <c r="V12" t="n">
         <v>1.788</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.1297</v>
+        <v>12.4325</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6977000000000015</v>
+        <v>-0.3948000000000009</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8272</v>
+        <v>12.8271</v>
       </c>
       <c r="G13" t="n">
         <v>16.4003</v>
@@ -1468,19 +1468,19 @@
         <v>9.701600000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6042</v>
+        <v>4.9069</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9294</v>
+        <v>-1.6266</v>
       </c>
       <c r="U13" t="n">
         <v>6.533399999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1432999999999998</v>
+        <v>-0.1433</v>
       </c>
       <c r="W13" t="n">
-        <v>4.9387</v>
+        <v>4.938700000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-5.0821</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1837</v>
+        <v>4.4295</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0323</v>
+        <v>3.3326</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1514</v>
+        <v>1.0969</v>
       </c>
       <c r="G14" t="n">
         <v>0.4433</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.679</v>
+        <v>-0.4332</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8479</v>
+        <v>-0.5476</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1689</v>
+        <v>0.1144</v>
       </c>
       <c r="V14" t="n">
         <v>2.091</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6142</v>
+        <v>1.2777</v>
       </c>
       <c r="E15" t="n">
-        <v>0.216</v>
+        <v>0.0158</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3982</v>
+        <v>1.262</v>
       </c>
       <c r="G15" t="n">
         <v>1.6784</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3701</v>
+        <v>0.0336</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.544</v>
+        <v>-0.7442</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9141</v>
+        <v>0.7778</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0164</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5567</v>
+        <v>0.8837</v>
       </c>
       <c r="E16" t="n">
         <v>1.6293</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0726</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.2082</v>
@@ -1702,13 +1702,13 @@
         <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5754</v>
+        <v>-1.2483</v>
       </c>
       <c r="T16" t="n">
         <v>-0.7257</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8497</v>
+        <v>-0.5226</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4045</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2498</v>
+        <v>0.1125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2675</v>
+        <v>-0.9525</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0177</v>
+        <v>1.0651</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8461</v>
+        <v>-0.1331</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8544</v>
+        <v>1.4797</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.7004</v>
+        <v>-1.6127</v>
       </c>
       <c r="J17" t="n">
-        <v>0.143</v>
+        <v>-0.3048</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3965</v>
+        <v>1.0298</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2535</v>
+        <v>-1.3347</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9891</v>
+        <v>0.1718</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5421</v>
+        <v>0.4498</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.4469</v>
+        <v>-0.2781</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5224</v>
+        <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8257</v>
+        <v>0.1396</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0946</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7311</v>
+        <v>0.7874</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2821</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0214</v>
+        <v>-1.2531</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1527</v>
+        <v>-0.4383</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1741</v>
+        <v>-0.8148</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1331</v>
+        <v>-3.3317</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4797</v>
+        <v>1.4253</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6127</v>
+        <v>-4.757</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3048</v>
+        <v>-0.6932</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0298</v>
+        <v>2.5623</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3347</v>
+        <v>-3.2555</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1718</v>
+        <v>-2.6385</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4498</v>
+        <v>-1.137</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2781</v>
+        <v>-1.5015</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0485</v>
+        <v>-0.8333</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8479</v>
+        <v>-0.6107</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8964</v>
+        <v>-0.2226</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2821</v>
+        <v>1.5537</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2821</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8809</v>
+        <v>-1.6238</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0389</v>
+        <v>-1.0338</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8421</v>
+        <v>-0.59</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3317</v>
+        <v>-2.8461</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4253</v>
+        <v>0.8544</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.757</v>
+        <v>-3.7004</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6932</v>
+        <v>0.143</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5623</v>
+        <v>1.3965</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.2555</v>
+        <v>-1.2535</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6385</v>
+        <v>-2.9891</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.137</v>
+        <v>-0.5421</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5015</v>
+        <v>-2.4469</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3284</v>
+        <v>2.5224</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4612</v>
+        <v>-0.048</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2113</v>
+        <v>-0.2067</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2499</v>
+        <v>0.1587</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5537</v>
+        <v>-0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2821</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7833</v>
+        <v>-2.4861</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3209</v>
+        <v>-3.3369</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4623</v>
+        <v>0.8508</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2995</v>
+        <v>-2.0591</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4482</v>
+        <v>0.627</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.7477</v>
+        <v>-2.686</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3283</v>
+        <v>-1.6189</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3182</v>
+        <v>0.3831</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6465</v>
+        <v>-2.002</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9712</v>
+        <v>-0.4402</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.87</v>
+        <v>0.2439</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1011</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2985</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2985</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.427</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6046</v>
+        <v>-0.7478</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2196</v>
+        <v>0.3208</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.9582</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8588</v>
+        <v>-2.6197</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.437</v>
+        <v>-1.3209</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5782</v>
+        <v>-1.2988</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0591</v>
+        <v>-3.2995</v>
       </c>
       <c r="H21" t="n">
-        <v>0.627</v>
+        <v>0.4482</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.686</v>
+        <v>-3.7477</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6189</v>
+        <v>-1.3283</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3831</v>
+        <v>1.3182</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.002</v>
+        <v>-2.6465</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4402</v>
+        <v>-1.9712</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2439</v>
+        <v>-0.87</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.1011</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.2985</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>3.2985</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7997</v>
+        <v>-0.6606</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8479</v>
+        <v>-0.6046</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0482</v>
+        <v>-0.0561</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.9582</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.5701</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9469</v>
+        <v>-3.8651</v>
       </c>
       <c r="E22" t="n">
         <v>-2.6078</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3391</v>
+        <v>-1.2573</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2041</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6846</v>
+        <v>-0.6029</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6057</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.079</v>
+        <v>0.0028</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2821</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2856</v>
+        <v>-6.9853</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.414899999999999</v>
+        <v>-8.114599999999999</v>
       </c>
       <c r="F23" t="n">
         <v>1.1293</v>
@@ -2248,10 +2248,10 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8244</v>
+        <v>-0.5241</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.393</v>
+        <v>-1.0927</v>
       </c>
       <c r="U23" t="n">
         <v>0.5687</v>
@@ -2287,7 +2287,7 @@
         <v>-12.8271</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6973999999999999</v>
+        <v>0.6977000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>-16.4004</v>
@@ -2317,7 +2317,7 @@
         <v>-10.2604</v>
       </c>
       <c r="P24" t="n">
-        <v>8.7315</v>
+        <v>8.731499999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-9.701799999999999</v>
@@ -2326,13 +2326,13 @@
         <v>18.4331</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.6041</v>
+        <v>-4.6042</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.5334</v>
+        <v>-6.533399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9292</v>
+        <v>1.9293</v>
       </c>
       <c r="V24" t="n">
         <v>0.1432000000000002</v>
